--- a/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-182501</t>
+          <t>I-167618</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,22 +503,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>GUADALUPE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-7.4245327</t>
+          <t>-7.2469025</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.5054396</t>
+          <t>-79.4630359</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jr. Transversal Áncash</t>
+          <t>Jirón San Eugenio / Prolongación Jirón Ayacucho</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-182502</t>
+          <t>I-167635</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,22 +555,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>GUADALUPE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-7.4245742</t>
+          <t>-7.2380262</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.5052182</t>
+          <t>-79.4686133</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jr. Transversal Áncash / Jr. Zepita</t>
+          <t>Avenida Manuel Seoane / Calle Manuel Escorza</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,12 +587,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-182546</t>
+          <t>I-167647</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,27 +607,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>GUADALUPE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-7.4240744</t>
+          <t>-7.2378057</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.5033121</t>
+          <t>-79.4688938</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Centenario / Jr. Manuel Herrera</t>
+          <t>Avenida Manuel Seoane / Jirón Unión</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-182549</t>
+          <t>I-167648</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,27 +659,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>GUADALUPE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-7.4240973</t>
+          <t>-7.2396372</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.5031118</t>
+          <t>-79.4648916</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Centenario / Jr. Manuel Herrera</t>
+          <t>Avenida Manuel Seoane / Calle Francisco Bolognesi</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-204874</t>
+          <t>I-167654</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,22 +711,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>GUADALUPE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-7.3861907</t>
+          <t>-7.2387432</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.4888848</t>
+          <t>-79.4677073</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Carretera San Pedro de Lloc - San José</t>
+          <t>Avenida Manuel Seoane / Jirón Justo Albújar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-204901</t>
+          <t>I-182546</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-7.3968741</t>
+          <t>-7.4240744</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.4989895</t>
+          <t>-79.5033121</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Carretera San Pedro de Lloc - San José</t>
+          <t>Avenida Centenario / Jirón Manuel Herrera</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-361342</t>
+          <t>I-204874</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,22 +820,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-7.4241738</t>
+          <t>-7.3861907</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.5030706</t>
+          <t>-79.4888848</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Centenario / Jr. Manuel Herrera</t>
+          <t>Carretera San Pedro de Lloc - San José / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-372209</t>
+          <t>I-123396</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130704</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,27 +867,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>PACASMAYO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-7.4237105</t>
+          <t>-7.4000164</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.5030689</t>
+          <t>-79.5630344</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Centenario</t>
+          <t>Avenida Gonzalo Ugas Salcedo / Calle Santa Rosa</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-706823</t>
+          <t>I-9294</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130704</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -919,27 +919,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>PACASMAYO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-7.370467</t>
+          <t>-7.3975022</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.4687355</t>
+          <t>-79.5675956</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,12 +951,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-706827</t>
+          <t>I-123404</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130704</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -971,30 +971,1018 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE LLOC</t>
+          <t>PACASMAYO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-7.3705641</t>
+          <t>-7.3998957</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.4687274</t>
+          <t>-79.566867</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-706823</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-7.370467</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-79.4687355</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-123509</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-7.4358113</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-79.5044723</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-725436</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-7.441964</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-79.5502297</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-737289</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-7.5834545</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-79.3786964</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-737291</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-7.5848876</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-79.3782941</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-737293</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-7.5848876</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-79.382363</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-737295</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-7.5864668</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-79.3797988</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-732522</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-7.4300602</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-79.5084316</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-737300</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-7.5888384</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-79.3792087</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-737301</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-7.5898806</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-79.3792167</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-737303</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-7.5904735</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-79.3805444</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-737323</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-7.5570609</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-79.3884108</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-737324</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-7.5787139</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-79.4099937</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-721201</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-7.3939924</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-79.5067278</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-637372</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-7.4605807</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-79.5192906</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-725417</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-7.448704</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-79.4715974</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-725457</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-7.5107281</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-79.5402967</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I-727974</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-7.4489261</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-79.4957346</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I-737298</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-7.5841843</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-79.3793522</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>130701</t>
         </is>

--- a/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1988,6 +1988,266 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>I-123511</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-7.4369713</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-79.5045681</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>I-737339</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-7.5800696</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-79.4143554</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>I-721205</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-7.39325</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-79.5082372</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>I-721206</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-7.3931389</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-79.5085214</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>I-721207</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SAN PEDRO DE LLOC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-7.3929329</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-79.5090484</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Manuel Seoane / Jirón Justo Albújar</t>
+          <t>Avenida Manuel Seoane / Calle López Albújar / Jirón Justo Albújar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2243,6 +2243,58 @@
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>130701</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>I-647083</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>130702</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GUADALUPE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-7.2510242</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-79.4978186</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Camino a la Playa Bocana / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>130701</t>
         </is>

--- a/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-167618</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>130702</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>GUADALUPE</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-7.2469025</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-167635</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>130702</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>GUADALUPE</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-7.2380262</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-167647</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>130702</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>GUADALUPE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-7.2378057</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-167648</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>130702</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>GUADALUPE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-7.2396372</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-167654</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130702</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>GUADALUPE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-7.2387432</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-182546</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-7.4240744</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-204874</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-7.3861907</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-123396</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>130704</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-7.4000164</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-9294</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>130704</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-7.3975022</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-123404</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>130704</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-7.3998957</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-706823</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-7.370467</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-123509</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-7.4358113</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-725436</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-7.441964</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-737289</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-7.5834545</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-737291</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-7.5848876</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-737293</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-7.5848876</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-737295</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-7.5864668</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-732522</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-7.4300602</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-737300</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-7.5888384</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-737301</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-7.5898806</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-737303</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-7.5904735</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-737323</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-7.5570609</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-737324</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-7.5787139</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-721201</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-7.3939924</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-637372</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-7.4605807</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-725417</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-7.448704</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-725457</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-7.5107281</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-727974</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-7.4489261</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-737298</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-7.5841843</t>
@@ -1980,40 +1835,35 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>I-123511</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-7.4369713</t>
@@ -2032,40 +1882,35 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>I-737339</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-7.5800696</t>
@@ -2084,40 +1929,35 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>I-721205</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-7.39325</t>
@@ -2136,40 +1976,35 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>I-721206</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-7.3931389</t>
@@ -2188,40 +2023,35 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>I-721207</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-7.3929329</t>
@@ -2240,40 +2070,35 @@
       <c r="I35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>130701</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PACASMAYO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SAN_PEDRO_DE_LLOC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>I-647083</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>130702</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>GUADALUPE</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-7.2510242</t>
@@ -2292,11 +2117,6 @@
       <c r="I36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>130701</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAN_PEDRO_DE_LLOC</t>
+          <t>SAN PEDRO DE LLOC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">

--- a/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-PACASMAYO-SAN_PEDRO_DE_LLOC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-167618</t>
+          <t>I-9294</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-7.2469025</t>
+          <t>-7.3975022</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.4630359</t>
+          <t>-79.5675956</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón San Eugenio / Prolongación Jirón Ayacucho</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-167635</t>
+          <t>I-741248</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-7.2380262</t>
+          <t>-7.433095</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.4686133</t>
+          <t>-79.5041331</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Manuel Seoane / Calle Manuel Escorza</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-167647</t>
+          <t>I-737339</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-7.2378057</t>
+          <t>-7.5800696</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.4688938</t>
+          <t>-79.4143554</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Manuel Seoane / Jirón Unión</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-167648</t>
+          <t>I-737324</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-7.2396372</t>
+          <t>-7.5787139</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.4648916</t>
+          <t>-79.4099937</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Manuel Seoane / Calle Francisco Bolognesi</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-167654</t>
+          <t>I-737323</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-7.2387432</t>
+          <t>-7.5570609</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.4677073</t>
+          <t>-79.3884108</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Manuel Seoane / Calle López Albújar / Jirón Justo Albújar</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -721,27 +721,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-182546</t>
+          <t>I-737303</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-7.4240744</t>
+          <t>-7.5904735</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.5033121</t>
+          <t>-79.3805444</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Centenario / Jirón Manuel Herrera</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -768,27 +768,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-204874</t>
+          <t>I-737301</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-7.3861907</t>
+          <t>-7.5898806</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.4888848</t>
+          <t>-79.3792167</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Carretera San Pedro de Lloc - San José / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-123396</t>
+          <t>I-737300</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-7.4000164</t>
+          <t>-7.5888384</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.5630344</t>
+          <t>-79.3792087</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Gonzalo Ugas Salcedo / Calle Santa Rosa</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-9294</t>
+          <t>I-737298</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-7.3975022</t>
+          <t>-7.5841843</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.5675956</t>
+          <t>-79.3793522</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-123404</t>
+          <t>I-737295</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-7.3998957</t>
+          <t>-7.5864668</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.566867</t>
+          <t>-79.3797988</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-706823</t>
+          <t>I-737293</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-7.370467</t>
+          <t>-7.5848876</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-79.4687355</t>
+          <t>-79.382363</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-123509</t>
+          <t>I-737291</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-7.4358113</t>
+          <t>-7.5848876</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-79.5044723</t>
+          <t>-79.3782941</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-725436</t>
+          <t>I-737289</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-7.441964</t>
+          <t>-7.5834545</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-79.5502297</t>
+          <t>-79.3786964</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-737289</t>
+          <t>I-732522</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-7.5834545</t>
+          <t>-7.4300602</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-79.3786964</t>
+          <t>-79.5084316</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-737291</t>
+          <t>I-727974</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-7.5848876</t>
+          <t>-7.4489261</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-79.3782941</t>
+          <t>-79.4957346</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-737293</t>
+          <t>I-725457</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-7.5848876</t>
+          <t>-7.5107281</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-79.382363</t>
+          <t>-79.5402967</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-737295</t>
+          <t>I-725436</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-7.5864668</t>
+          <t>-7.441964</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-79.3797988</t>
+          <t>-79.5502297</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-732522</t>
+          <t>I-725417</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-7.4300602</t>
+          <t>-7.448704</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-79.5084316</t>
+          <t>-79.4715974</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-737300</t>
+          <t>I-721207</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-7.5888384</t>
+          <t>-7.3929329</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-79.3792087</t>
+          <t>-79.5090484</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-737301</t>
+          <t>I-721206</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-7.5898806</t>
+          <t>-7.3931389</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-79.3792167</t>
+          <t>-79.5085214</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-737303</t>
+          <t>I-721205</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-7.5904735</t>
+          <t>-7.39325</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-79.3805444</t>
+          <t>-79.5082372</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-737323</t>
+          <t>I-721201</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-7.5570609</t>
+          <t>-7.3939924</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-79.3884108</t>
+          <t>-79.5067278</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-737324</t>
+          <t>I-706823</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-7.5787139</t>
+          <t>-7.370467</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-79.4099937</t>
+          <t>-79.4687355</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-721201</t>
+          <t>I-647083</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-7.3939924</t>
+          <t>-7.2510242</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-79.5067278</t>
+          <t>-79.4978186</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Camino a la Playa Bocana / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1661,22 +1661,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-725417</t>
+          <t>I-372210</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-7.448704</t>
+          <t>-7.4248195</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.4715974</t>
+          <t>-79.5031035</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-725457</t>
+          <t>I-361344</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-7.5107281</t>
+          <t>-7.4322702</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-79.5402967</t>
+          <t>-79.5040319</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-727974</t>
+          <t>I-361342</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-7.4489261</t>
+          <t>-7.4241738</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-79.4957346</t>
+          <t>-79.5030706</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-737298</t>
+          <t>I-361321</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-7.5841843</t>
+          <t>-7.4226352</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-79.3793522</t>
+          <t>-79.5031851</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,27 +1849,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-123511</t>
+          <t>I-204874</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-7.4369713</t>
+          <t>-7.3861907</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-79.5045681</t>
+          <t>-79.4888848</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Carretera San Pedro de Lloc - San José / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1896,22 +1896,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-737339</t>
+          <t>I-182549</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-7.5800696</t>
+          <t>-7.4240973</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-79.4143554</t>
+          <t>-79.5031118</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1943,27 +1943,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-721205</t>
+          <t>I-182546</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-7.39325</t>
+          <t>-7.4240744</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-79.5082372</t>
+          <t>-79.5033121</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Centenario / Jirón Manuel Herrera</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1990,27 +1990,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-721206</t>
+          <t>I-167654</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-7.3931389</t>
+          <t>-7.2387432</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-79.5085214</t>
+          <t>-79.4677073</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Manuel Seoane / Jirón Justo Albújar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2037,27 +2037,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-721207</t>
+          <t>I-167648</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-7.3929329</t>
+          <t>-7.2396372</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-79.5090484</t>
+          <t>-79.4648916</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Manuel Seoane / Calle Francisco Bolognesi</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2084,27 +2084,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-647083</t>
+          <t>I-167647</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-7.2510242</t>
+          <t>-7.2378057</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-79.4978186</t>
+          <t>-79.4688938</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Camino a la Playa Bocana / Calle s / n</t>
+          <t>Avenida Manuel Seoane / Jirón Unión</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2131,27 +2131,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-123511</t>
+          <t>I-167635</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-7.4369713</t>
+          <t>-7.2380262</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-79.5045681</t>
+          <t>-79.4686133</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Manuel Seoane / Calle Manuel Escorza</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2178,27 +2178,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-123510</t>
+          <t>I-167618</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-7.4362542</t>
+          <t>-7.2469025</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-79.5045176</t>
+          <t>-79.4630359</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Jirón San Eugenio / Prolongación Jirón Ayacucho</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2225,22 +2225,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-123509</t>
+          <t>I-123542</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-7.4358113</t>
+          <t>-7.4251363</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-79.5044723</t>
+          <t>-79.5033271</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>I-123513</t>
+          <t>I-123540</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-7.434523</t>
+          <t>-7.4272959</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-79.5043272</t>
+          <t>-79.5035331</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2319,22 +2319,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>I-123512</t>
+          <t>I-123539</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-7.4338036</t>
+          <t>-7.4317995</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-79.5042462</t>
+          <t>-79.5039811</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>I-741248</t>
+          <t>I-123538</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-7.433095</t>
+          <t>-7.4254442</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-79.5041331</t>
+          <t>-79.5033586</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2413,17 +2413,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>I-361344</t>
+          <t>I-123537</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-7.4322702</t>
+          <t>-7.4287876</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-79.5040319</t>
+          <t>-79.5036816</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>I-123539</t>
+          <t>I-123513</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-7.4317995</t>
+          <t>-7.434523</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-79.5039811</t>
+          <t>-79.5043272</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2554,22 +2554,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>I-123537</t>
+          <t>I-123512</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-7.4287876</t>
+          <t>-7.4338036</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-79.5036816</t>
+          <t>-79.5042462</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2601,22 +2601,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>I-361321</t>
+          <t>I-123511</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-7.4226352</t>
+          <t>-7.4369713</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-79.5031851</t>
+          <t>-79.5045681</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>I-182546</t>
+          <t>I-123510</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-7.4240744</t>
+          <t>-7.4362542</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-79.5033121</t>
+          <t>-79.5045176</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Avenida Centenario / Jirón Manuel Herrera</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2695,22 +2695,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>I-182549</t>
+          <t>I-123509</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-7.4240973</t>
+          <t>-7.4358113</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-79.5031118</t>
+          <t>-79.5044723</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2742,22 +2742,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>I-372210</t>
+          <t>I-123404</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-7.4248195</t>
+          <t>-7.3998957</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-79.5031035</t>
+          <t>-79.566867</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2789,168 +2789,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>I-123542</t>
+          <t>I-123396</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-7.4251363</t>
+          <t>-7.4000164</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-79.5033271</t>
+          <t>-79.5630344</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Avenida Gonzalo Ugas Salcedo / Calle Santa Rosa</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>I-361342</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-7.4241738</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-79.5030706</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>calle sn / calle s/n</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>I-123540</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-7.4272959</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-79.5035331</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Calle s / n / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>130701</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>PACASMAYO</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SAN PEDRO DE LLOC</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>I-123538</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-7.4254442</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-79.5033586</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Calle s / n / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
